--- a/InputData/elec/HCFoTC/Hard Cap Frac of Total Capacity.xlsx
+++ b/InputData/elec/HCFoTC/Hard Cap Frac of Total Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\elec\HCFoTC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\ND\elec\HCFoTC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8D0CE3-CBFC-4D0A-8776-52CEC165498F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57B55CE6-F90E-4EB1-91D3-95E52371B5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>Source:</t>
   </si>
@@ -179,6 +179,231 @@
   </si>
   <si>
     <t>Unit: dimensionless (%)</t>
+  </si>
+  <si>
+    <t>## HCFoTC: uniform 22% (draft, 2026-08-04)</t>
+  </si>
+  <si>
+    <t>### Basis</t>
+  </si>
+  <si>
+    <t>For each state and year, we computed the annual build share:</t>
+  </si>
+  <si>
+    <t>`share(t) = capacity additions(t) ÷ operating fleet(t−1)`, from an EIA-860</t>
+  </si>
+  <si>
+    <t>generator panel (2025 Early Release, Operable + Retired sheets, 1990–2025,</t>
+  </si>
+  <si>
+    <t>nameplate MW). Storage, pumped hydro, and industrial byproduct-fuel units are</t>
+  </si>
+  <si>
+    <t>excluded; retired and canceled units that never operated are dropped. The share</t>
+  </si>
+  <si>
+    <t>series per state is in `staging/hcfotc_shares.csv`.</t>
+  </si>
+  <si>
+    <t>Two bases were computed:</t>
+  </si>
+  <si>
+    <t>- **Total additions ÷ fleet** — the basis in the original Phase 1 plan.</t>
+  </si>
+  <si>
+    <t>- **Per-source additions ÷ fleet** — the basis the model actually applies (see</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "Structural correction" below). This is the like-for-like target.</t>
+  </si>
+  <si>
+    <t>| percentile of state maxima | total basis | per-source basis |</t>
+  </si>
+  <si>
+    <t>|---|---|---|</t>
+  </si>
+  <si>
+    <t>| p25 | 10.6% | 8.1% |</t>
+  </si>
+  <si>
+    <t>| median | 12.3% | 11.0% |</t>
+  </si>
+  <si>
+    <t>| p75 | 16.8% | 14.1% |</t>
+  </si>
+  <si>
+    <t>| p90 | 21.4% | 19.9% |</t>
+  </si>
+  <si>
+    <t>### Why one uniform value instead of 48</t>
+  </si>
+  <si>
+    <t>The cross-state spread largely does not measure state capability.</t>
+  </si>
+  <si>
+    <t>1. **It is one historical event repeated.** On the per-source basis, 9 of the 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   highest state maxima are the same event — the 2000–2003 combined-cycle gas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   boom, in different years. That was a national supply-chain wave. A per-state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   cap derived from it encodes which states received gas plants in 2002, not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   which states can build quickly.</t>
+  </si>
+  <si>
+    <t>2. **The remaining spread is fleet size.** Rhode Island's 108% (1991) and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Maine's 35% (2000) reflect small denominators, not superior capability: one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ordinary combined-cycle plant is a large share of a small fleet. Per-state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ratios preserve that artifact rather than correcting it.</t>
+  </si>
+  <si>
+    <t>Both points follow from the project's own premise that states borrow supply</t>
+  </si>
+  <si>
+    <t>chains from the national market, which argues for a shared value.</t>
+  </si>
+  <si>
+    <t>### Why 22%</t>
+  </si>
+  <si>
+    <t>22% is approximately the p90 of the per-source distribution, rounded up. It is</t>
+  </si>
+  <si>
+    <t>the lowest round value that does not cap a state below a build rate it has</t>
+  </si>
+  <si>
+    <t>actually achieved, except in three explainable cases.</t>
+  </si>
+  <si>
+    <t>| candidate | states capped below demonstrated history (per-source basis) |</t>
+  </si>
+  <si>
+    <t>|---|---|</t>
+  </si>
+  <si>
+    <t>| 4% (shipped national value) | 47 of 48 |</t>
+  </si>
+  <si>
+    <t>| 17% (p75, total basis) | 8 — AZ, AR, LA, MS, NH, NM, RI, ME |</t>
+  </si>
+  <si>
+    <t>| **22%** | **3 — RI and ME (pre-2002, understated denominators), MS (2003 gas boom)** |</t>
+  </si>
+  <si>
+    <t>Erring high is deliberate, because the error is asymmetric. A cap set too tight</t>
+  </si>
+  <si>
+    <t>distorts visibly: in the MI BAU baseline, solar PV was hard-cap-clipped in three</t>
+  </si>
+  <si>
+    <t>years and the RPS requirement overflowed into biomass and municipal solid waste,</t>
+  </si>
+  <si>
+    <t>each built to its full resource ceiling. A cap set too loose is largely inert,</t>
+  </si>
+  <si>
+    <t>because `SCGF` (per-source growth) and `MPCbS` (resource potential) are the</t>
+  </si>
+  <si>
+    <t>binding constraints in practice. The hard cap's function is to prevent</t>
+  </si>
+  <si>
+    <t>implausible single-source spikes, not to fine-tune the build trajectory.</t>
+  </si>
+  <si>
+    <t>Small states are protected structurally rather than by the cap: the build limit</t>
+  </si>
+  <si>
+    <t>is `MAX(MIN(hard cap, soft cap), Minimum Buildable Capacity)`, where the floor is</t>
+  </si>
+  <si>
+    <t>`MAX(2% of fleet, MPPC)`. One minimum-size plant remains buildable at any cap</t>
+  </si>
+  <si>
+    <t>value (Vermont: 193 MW per source at 22%, against a fleet of 878 MW).</t>
+  </si>
+  <si>
+    <t>### Structural correction to the Phase 1 method</t>
+  </si>
+  <si>
+    <t>`Annual Electricity Capacity Build Hard Cap` is an **unsubscripted scalar**</t>
+  </si>
+  <si>
+    <t>(`total fleet × HCFoTC`) consumed inside `MIN(hard cap, soft cap[source])`. It</t>
+  </si>
+  <si>
+    <t>therefore caps **each source individually**, not total annual additions.</t>
+  </si>
+  <si>
+    <t>Verified in the MI BAU run: 2041 additions totaled 6,200 MW against a 2,082 MW</t>
+  </si>
+  <si>
+    <t>hard cap, with five sources each clipped near that value.</t>
+  </si>
+  <si>
+    <t>Two implications:</t>
+  </si>
+  <si>
+    <t>- The calibration target is the per-source share, not the total share. A value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  derived from total additions is more permissive than the model requires; the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  difference is headroom, and should be recorded as such rather than assumed.</t>
+  </si>
+  <si>
+    <t>- No variable in the model constrains total annual additions. Aggregate build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  realism cannot be delivered through `HCFoTC`; that is a Tier-2 structural item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  for the model development team.</t>
+  </si>
+  <si>
+    <t>### Caveats</t>
+  </si>
+  <si>
+    <t>- The panel is **nameplate** capacity; EPS capacity is **net summer**. Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ratios are basis-insensitive, but any absolute-MW comparison to EPS variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  must state the basis on both sides.</t>
+  </si>
+  <si>
+    <t>- EIA-860's retired-generator coverage thins before ~2002 (220 of 4,697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  retirements predate it), so early-window fleet denominators are understated and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  those shares overstated. Both states clipped at 22% for pre-2002 reasons (RI,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ME) fall in this window.</t>
+  </si>
+  <si>
+    <t>- Values are draft pending staff review; the underlying figures should be</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  verified against EIA primary sources before use in any published work product.</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
   </si>
 </sst>
 </file>
@@ -268,7 +493,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma 2" xfId="5" xr:uid="{68733429-A9FA-4187-B93D-3BEA15728D17}"/>
@@ -724,18 +949,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667665C7-8A8E-46D9-B686-64BA7741F669}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="73.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="3">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,19 +974,389 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +1389,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
